--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92545227433</v>
+        <v>46157.93120967515</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120967515</v>
+        <v>46157.93372156914</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93372156914</v>
+        <v>46157.93678748645</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93678748645</v>
+        <v>46158.28198162009</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28198162009</v>
+        <v>46158.29724242948</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29724242948</v>
+        <v>46158.29795041683</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29795041683</v>
+        <v>46158.33359568066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33359568066</v>
+        <v>46158.37213048538</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.2 Путевые листы 2025/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37213048538</v>
+        <v>46158.37269780998</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
